--- a/KAMCHATKA_FINAL_ZAPOLNENIE.xlsx
+++ b/KAMCHATKA_FINAL_ZAPOLNENIE.xlsx
@@ -34084,7 +34084,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F3" s="276" t="inlineStr"/>
+      <c r="F3" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G3" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -34136,7 +34140,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F4" s="276" t="inlineStr"/>
+      <c r="F4" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G4" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -34188,7 +34196,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F5" s="276" t="inlineStr"/>
+      <c r="F5" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G5" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -38136,7 +38148,11 @@
           <t>ООО «Бологовский арматурный завод» (ТМ «БАЗ», латунная арматура)</t>
         </is>
       </c>
-      <c r="F78" s="276" t="inlineStr"/>
+      <c r="F78" s="276" t="inlineStr">
+        <is>
+          <t>+7 (48238) 2-21-13 (завод, Бологое) sales@bolarm.com (продажи)</t>
+        </is>
+      </c>
       <c r="G78" s="276" t="inlineStr">
         <is>
           <t>15б1п Ду15 латунный муфтовый</t>
@@ -38192,7 +38208,11 @@
           <t>ООО «Бологовский арматурный завод» (ТМ «БАЗ», латунная арматура)</t>
         </is>
       </c>
-      <c r="F79" s="276" t="inlineStr"/>
+      <c r="F79" s="276" t="inlineStr">
+        <is>
+          <t>+7 (48238) 2-21-13 (завод, Бологое) sales@bolarm.com (продажи)</t>
+        </is>
+      </c>
       <c r="G79" s="276" t="inlineStr">
         <is>
           <t>15б1п Ду20 латунный муфтовый</t>
@@ -38248,7 +38268,11 @@
           <t>ООО «Бологовский арматурный завод» (ТМ «БАЗ», латунная арматура)</t>
         </is>
       </c>
-      <c r="F80" s="276" t="inlineStr"/>
+      <c r="F80" s="276" t="inlineStr">
+        <is>
+          <t>+7 (48238) 2-21-13 (завод, Бологое) sales@bolarm.com (продажи)</t>
+        </is>
+      </c>
       <c r="G80" s="276" t="inlineStr">
         <is>
           <t>15б1п Ду25 латунный муфтовый</t>
@@ -38304,7 +38328,11 @@
           <t>ООО «Бологовский арматурный завод» (ТМ «БАЗ», латунная арматура)</t>
         </is>
       </c>
-      <c r="F81" s="276" t="inlineStr"/>
+      <c r="F81" s="276" t="inlineStr">
+        <is>
+          <t>+7 (48238) 2-21-13 (завод, Бологое) sales@bolarm.com (продажи)</t>
+        </is>
+      </c>
       <c r="G81" s="276" t="inlineStr">
         <is>
           <t>15б1п Ду32 латунный муфтовый</t>
@@ -38360,7 +38388,11 @@
           <t>ООО «Бологовский арматурный завод» (ТМ «БАЗ», латунная арматура)</t>
         </is>
       </c>
-      <c r="F82" s="276" t="inlineStr"/>
+      <c r="F82" s="276" t="inlineStr">
+        <is>
+          <t>+7 (48238) 2-21-13 (завод, Бологое) sales@bolarm.com (продажи)</t>
+        </is>
+      </c>
       <c r="G82" s="276" t="inlineStr">
         <is>
           <t>15б1п Ду40 латунный муфтовый</t>
@@ -38416,7 +38448,11 @@
           <t>ООО «Бологовский арматурный завод» (ТМ «БАЗ», латунная арматура)</t>
         </is>
       </c>
-      <c r="F83" s="276" t="inlineStr"/>
+      <c r="F83" s="276" t="inlineStr">
+        <is>
+          <t>+7 (48238) 2-21-13 (завод, Бологое) sales@bolarm.com (продажи)</t>
+        </is>
+      </c>
       <c r="G83" s="276" t="inlineStr">
         <is>
           <t>15б1п Ду50 латунный муфтовый</t>
@@ -38472,7 +38508,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F84" s="276" t="inlineStr"/>
+      <c r="F84" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G84" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -38524,7 +38564,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F85" s="276" t="inlineStr"/>
+      <c r="F85" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G85" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -38640,7 +38684,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F88" s="276" t="inlineStr"/>
+      <c r="F88" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G88" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -38692,7 +38740,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F89" s="276" t="inlineStr"/>
+      <c r="F89" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G89" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -38744,7 +38796,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F90" s="276" t="inlineStr"/>
+      <c r="F90" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G90" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -38796,7 +38852,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F91" s="276" t="inlineStr"/>
+      <c r="F91" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G91" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -38848,7 +38908,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F92" s="276" t="inlineStr"/>
+      <c r="F92" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G92" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -38900,7 +38964,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F93" s="276" t="inlineStr"/>
+      <c r="F93" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G93" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -40628,7 +40696,11 @@
           <t>ООО ПИК «АЛГРУПП»</t>
         </is>
       </c>
-      <c r="F123" s="276" t="inlineStr"/>
+      <c r="F123" s="276" t="inlineStr">
+        <is>
+          <t>8-800-200-52-76 info@pik-algrupp.ru</t>
+        </is>
+      </c>
       <c r="G123" s="276" t="inlineStr">
         <is>
           <t>Задвижка чугунная параллельная литая PN 0,6-1,6 МПа DN 50-400 мм</t>
@@ -40680,7 +40752,11 @@
           <t>ООО ПИК «АЛГРУПП»</t>
         </is>
       </c>
-      <c r="F124" s="276" t="inlineStr"/>
+      <c r="F124" s="276" t="inlineStr">
+        <is>
+          <t>8-800-200-52-76 info@pik-algrupp.ru</t>
+        </is>
+      </c>
       <c r="G124" s="276" t="inlineStr">
         <is>
           <t>Задвижка чугунная параллельная литая PN 0,6-1,6 МПа DN 50-400 мм</t>
@@ -40732,7 +40808,11 @@
           <t>ООО ПИК «АЛГРУПП»</t>
         </is>
       </c>
-      <c r="F125" s="276" t="inlineStr"/>
+      <c r="F125" s="276" t="inlineStr">
+        <is>
+          <t>8-800-200-52-76 info@pik-algrupp.ru</t>
+        </is>
+      </c>
       <c r="G125" s="276" t="inlineStr">
         <is>
           <t>Задвижка чугунная параллельная литая PN 0,6-1,6 МПа DN 50-400 мм</t>
@@ -40784,7 +40864,11 @@
           <t>ООО ПИК «АЛГРУПП»</t>
         </is>
       </c>
-      <c r="F126" s="276" t="inlineStr"/>
+      <c r="F126" s="276" t="inlineStr">
+        <is>
+          <t>8-800-200-52-76 info@pik-algrupp.ru</t>
+        </is>
+      </c>
       <c r="G126" s="276" t="inlineStr">
         <is>
           <t>Задвижка чугунная параллельная литая PN 0,6-1,6 МПа DN 50-400 мм</t>
@@ -40836,7 +40920,11 @@
           <t>ООО ПИК «АЛГРУПП»</t>
         </is>
       </c>
-      <c r="F127" s="276" t="inlineStr"/>
+      <c r="F127" s="276" t="inlineStr">
+        <is>
+          <t>8-800-200-52-76 info@pik-algrupp.ru</t>
+        </is>
+      </c>
       <c r="G127" s="276" t="inlineStr">
         <is>
           <t>Задвижка чугунная параллельная литая PN 0,6-1,6 МПа DN 50-400 мм</t>
@@ -40888,7 +40976,11 @@
           <t>ООО ПИК «АЛГРУПП»</t>
         </is>
       </c>
-      <c r="F128" s="276" t="inlineStr"/>
+      <c r="F128" s="276" t="inlineStr">
+        <is>
+          <t>8-800-200-52-76 info@pik-algrupp.ru</t>
+        </is>
+      </c>
       <c r="G128" s="276" t="inlineStr">
         <is>
           <t>Задвижка чугунная параллельная литая PN 0,6-1,6 МПа DN 50-400 мм</t>
@@ -40940,7 +41032,11 @@
           <t>ООО ПИК «АЛГРУПП»</t>
         </is>
       </c>
-      <c r="F129" s="276" t="inlineStr"/>
+      <c r="F129" s="276" t="inlineStr">
+        <is>
+          <t>8-800-200-52-76 info@pik-algrupp.ru</t>
+        </is>
+      </c>
       <c r="G129" s="276" t="inlineStr">
         <is>
           <t>Задвижка чугунная параллельная литая PN 0,6-1,6 МПа DN 50-400 мм</t>
@@ -45908,7 +46004,11 @@
           <t>ООО ПКФ «Экс-Форма»</t>
         </is>
       </c>
-      <c r="F222" s="276" t="inlineStr"/>
+      <c r="F222" s="276" t="inlineStr">
+        <is>
+          <t>8-800-550-52-31 exform@exform.ru</t>
+        </is>
+      </c>
       <c r="G222" s="276" t="inlineStr">
         <is>
           <t>ПСК-50С/125</t>
@@ -46296,7 +46396,11 @@
           <t>ООО «Бологовский арматурный завод» (ТМ «БАЗ», латунная арматура)</t>
         </is>
       </c>
-      <c r="F229" s="276" t="inlineStr"/>
+      <c r="F229" s="276" t="inlineStr">
+        <is>
+          <t>+7 (48238) 2-21-13 (завод, Бологое) sales@bolarm.com (продажи)</t>
+        </is>
+      </c>
       <c r="G229" s="276" t="inlineStr">
         <is>
           <t>15б1п Ду15 латунный муфтовый</t>
@@ -46352,7 +46456,11 @@
           <t>ООО «Бологовский арматурный завод» (ТМ «БАЗ», латунная арматура)</t>
         </is>
       </c>
-      <c r="F230" s="276" t="inlineStr"/>
+      <c r="F230" s="276" t="inlineStr">
+        <is>
+          <t>+7 (48238) 2-21-13 (завод, Бологое) sales@bolarm.com (продажи)</t>
+        </is>
+      </c>
       <c r="G230" s="276" t="inlineStr">
         <is>
           <t>15б1п Ду20 латунный муфтовый</t>
@@ -46408,7 +46516,11 @@
           <t>ООО «Бологовский арматурный завод» (ТМ «БАЗ», латунная арматура)</t>
         </is>
       </c>
-      <c r="F231" s="276" t="inlineStr"/>
+      <c r="F231" s="276" t="inlineStr">
+        <is>
+          <t>+7 (48238) 2-21-13 (завод, Бологое) sales@bolarm.com (продажи)</t>
+        </is>
+      </c>
       <c r="G231" s="276" t="inlineStr">
         <is>
           <t>15б1п Ду25 латунный муфтовый</t>
@@ -47116,7 +47228,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F244" s="276" t="inlineStr"/>
+      <c r="F244" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G244" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -47168,7 +47284,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F245" s="276" t="inlineStr"/>
+      <c r="F245" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G245" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -47220,7 +47340,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F246" s="276" t="inlineStr"/>
+      <c r="F246" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G246" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -47272,7 +47396,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F247" s="276" t="inlineStr"/>
+      <c r="F247" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G247" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -47324,7 +47452,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F248" s="276" t="inlineStr"/>
+      <c r="F248" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G248" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -47376,7 +47508,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F249" s="276" t="inlineStr"/>
+      <c r="F249" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G249" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -47428,7 +47564,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F250" s="276" t="inlineStr"/>
+      <c r="F250" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G250" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -47480,7 +47620,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F251" s="276" t="inlineStr"/>
+      <c r="F251" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G251" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -47532,7 +47676,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="F252" s="276" t="inlineStr"/>
+      <c r="F252" s="276" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="G252" s="276" t="inlineStr">
         <is>
           <t>Клапаны запорные DN 10-400 мм, PN 0,6-50,0 МПа</t>
@@ -47944,7 +48092,11 @@
           <t>ООО ПИК «АЛГРУПП»</t>
         </is>
       </c>
-      <c r="F259" s="276" t="inlineStr"/>
+      <c r="F259" s="276" t="inlineStr">
+        <is>
+          <t>8-800-200-52-76 info@pik-algrupp.ru</t>
+        </is>
+      </c>
       <c r="G259" s="276" t="inlineStr">
         <is>
           <t>Задвижка чугунная параллельная литая PN 0,6-1,6 МПа DN 50-400 мм</t>
@@ -47996,7 +48148,11 @@
           <t>ООО ПИК «АЛГРУПП»</t>
         </is>
       </c>
-      <c r="F260" s="276" t="inlineStr"/>
+      <c r="F260" s="276" t="inlineStr">
+        <is>
+          <t>8-800-200-52-76 info@pik-algrupp.ru</t>
+        </is>
+      </c>
       <c r="G260" s="276" t="inlineStr">
         <is>
           <t>Задвижка чугунная параллельная литая PN 0,6-1,6 МПа DN 50-400 мм</t>
@@ -48048,7 +48204,11 @@
           <t>ООО ПИК «АЛГРУПП»</t>
         </is>
       </c>
-      <c r="F261" s="276" t="inlineStr"/>
+      <c r="F261" s="276" t="inlineStr">
+        <is>
+          <t>8-800-200-52-76 info@pik-algrupp.ru</t>
+        </is>
+      </c>
       <c r="G261" s="276" t="inlineStr">
         <is>
           <t>Задвижка чугунная параллельная литая PN 0,6-1,6 МПа DN 50-400 мм</t>
